--- a/results/Int Task Remove ACC -0.6/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_7_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6674360419765484</v>
+        <v>0.6522224248625467</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6660386132454137</v>
+        <v>0.6522224248625467</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6665975847378676</v>
+        <v>0.6522224248625467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7080883885515059</v>
+        <v>0.6522224248625467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6988245018995557</v>
+        <v>0.6522224248625467</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6988245018995557</v>
+        <v>0.654973662021203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6983691533003002</v>
+        <v>0.6482946237679732</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6938373787710839</v>
+        <v>0.6482946237679732</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6906171740043519</v>
+        <v>0.6531645049944261</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.690058202511898</v>
+        <v>0.6629492693895209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6684355587978007</v>
+        <v>0.6580643875156718</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6439880563266415</v>
+        <v>0.6579321449662564</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.636602803384146</v>
+        <v>0.6444840645754185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6369709113761751</v>
+        <v>0.6481323799237652</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6416199278074106</v>
+        <v>0.6597399203544574</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6408550921671357</v>
+        <v>0.6606669998389404</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6101280423681443</v>
+        <v>0.6640780681060972</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6019029505483922</v>
+        <v>0.6702145171528455</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6059329928975883</v>
+        <v>0.6794853119976757</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6076576725942909</v>
+        <v>0.7019477945890296</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6018184732183178</v>
+        <v>0.7005203645631022</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6018184732183178</v>
+        <v>0.6840784707550537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5641629007146625</v>
+        <v>0.6667067341853701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5579555933466602</v>
+        <v>0.6755766564662264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5579555933466602</v>
+        <v>0.6653365434718761</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5246612616965575</v>
+        <v>0.6491032770888007</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5298120103078132</v>
+        <v>0.6533705665191867</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5519350045633549</v>
+        <v>0.6508701954505405</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5232419241251465</v>
+        <v>0.6491646613169622</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5113304232077385</v>
+        <v>0.6120080577161751</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5647899672512182</v>
+        <v>0.5832755018900816</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5571007538220071</v>
+        <v>0.5820539360119753</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5490542881324352</v>
+        <v>0.5818480718641541</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.551864146242101</v>
+        <v>0.5547707190520854</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5864114267036789</v>
+        <v>0.5632289130372995</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5722598949007273</v>
+        <v>0.5735848862950927</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5858702191357732</v>
+        <v>0.5909935323524489</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5769566765513038</v>
+        <v>0.5839286221826415</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5938008245619022</v>
+        <v>0.5718807338000903</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5863283310121805</v>
+        <v>0.5542703685106409</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5907264813534058</v>
+        <v>0.5082219337887215</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5590873527173278</v>
+        <v>0.5079424480424946</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5419350993042857</v>
+        <v>0.5403574654274553</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5447149561191589</v>
+        <v>0.4989430464893748</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5488186200667609</v>
+        <v>0.5267349038221649</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5406399118277736</v>
+        <v>0.5563509188291285</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5356077867571127</v>
+        <v>0.5563509188291285</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.54403736108611</v>
+        <v>0.5735945577651246</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5288728908300253</v>
+        <v>0.5675058739377173</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5259307901709442</v>
+        <v>0.591248543358187</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5311101584384168</v>
+        <v>0.5603604339766243</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5328456938667879</v>
+        <v>0.5555505553397568</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5330815593094018</v>
+        <v>0.5783497629897711</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.533007937710996</v>
+        <v>0.5718971160860626</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5363617666657192</v>
+        <v>0.5639106529860762</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5781632417820137</v>
+        <v>0.5688296810704463</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5781632417820137</v>
+        <v>0.5326915424770964</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.585297628634499</v>
+        <v>0.5315735994921886</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5812825869326992</v>
+        <v>0.523823001834816</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5853562495855085</v>
+        <v>0.5319089429122731</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5992119133562607</v>
+        <v>0.501589476493196</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5992119133562607</v>
+        <v>0.5021184466908571</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6521941999602088</v>
+        <v>0.5021184466908571</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6532235206993144</v>
+        <v>0.5029624304838419</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6584301269844277</v>
+        <v>0.4998458486103085</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6552235412265162</v>
+        <v>0.5160710225388674</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6434115182865787</v>
+        <v>0.5054355635348473</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6442349748778632</v>
+        <v>0.5153048052600164</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6439704897790326</v>
+        <v>0.514319104824524</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6245862979349635</v>
+        <v>0.4804616567662394</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.651140207103675</v>
+        <v>0.5138009903585312</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6102166646139465</v>
+        <v>0.527437170972642</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6215283370124395</v>
+        <v>0.5170961983622451</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6255583793616356</v>
+        <v>0.5323248161236432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6255583793616356</v>
+        <v>0.5400931777055642</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6255583793616356</v>
+        <v>0.5374619457260787</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6335298418142257</v>
+        <v>0.5033700138637562</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5364215718783653</v>
+        <v>0.485207585274733</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5234371299182385</v>
+        <v>0.4864755347336043</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.528804598408984</v>
+        <v>0.4828994593450875</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5185972499865783</v>
+        <v>0.4981880796960711</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5116945836609791</v>
+        <v>0.4982617012944769</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5588649089065949</v>
+        <v>0.4986420466567504</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.558585423160368</v>
+        <v>0.4747274619220408</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5319659848477671</v>
+        <v>0.4747274619220408</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5007668094096692</v>
+        <v>0.4567162240686177</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4960850284064892</v>
+        <v>0.4921045276690889</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5054703018761862</v>
+        <v>0.4921209099550612</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5024573428958513</v>
+        <v>0.4936055792934221</v>
       </c>
     </row>
   </sheetData>
